--- a/programRuleVariable_to_programRuleVariable_post_new.xlsx
+++ b/programRuleVariable_to_programRuleVariable_post_new.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_script_pirama_production\python_dhis2_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC036B40-493B-43AD-A863-2DF818F111DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BADA85-7F5C-4991-8E26-4E32827762E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9D052B52-B6E2-47A1-9FEC-25002631EBA3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="238">
   <si>
     <t>program</t>
   </si>
@@ -47,110 +47,716 @@
     <t>programruleVariable_to</t>
   </si>
   <si>
-    <t>FrCiBHAumZB</t>
-  </si>
-  <si>
-    <t>u4GBCBEkoqe</t>
-  </si>
-  <si>
-    <t>p5bdietM9XK</t>
-  </si>
-  <si>
-    <t>C2BrSC29mJL</t>
-  </si>
-  <si>
-    <t>iJjBdBpcaj8</t>
-  </si>
-  <si>
-    <t>JsdcWSalJyU</t>
-  </si>
-  <si>
-    <t>ZPtlPVQrlcO</t>
-  </si>
-  <si>
-    <t>T6yy0GXVVsr</t>
-  </si>
-  <si>
-    <t>U8XH5kDsZ7f</t>
-  </si>
-  <si>
-    <t>wSPQT4iWDRf</t>
-  </si>
-  <si>
-    <t>bpkFh4DRbMa</t>
-  </si>
-  <si>
-    <t>MXQkrh56xHd</t>
-  </si>
-  <si>
-    <t>TfI92UmWyaW</t>
-  </si>
-  <si>
-    <t>qdI0hogzV1Y</t>
-  </si>
-  <si>
-    <t>m8F556DT8Q1</t>
-  </si>
-  <si>
-    <t>jjodhZJUWkE</t>
-  </si>
-  <si>
-    <t>GxL0iRgjm4n</t>
-  </si>
-  <si>
-    <t>Tc0opItZwAM</t>
-  </si>
-  <si>
-    <t>WBM3nmD0nJq</t>
-  </si>
-  <si>
-    <t>WghXjTrCBNY</t>
-  </si>
-  <si>
-    <t>JmOHHkEriEs</t>
-  </si>
-  <si>
-    <t>wBVOEVBXJvH</t>
-  </si>
-  <si>
-    <t>O5AVnLGDPYH</t>
-  </si>
-  <si>
-    <t>v3s72jQhkgv</t>
-  </si>
-  <si>
-    <t>TJvRx0xwBpt</t>
-  </si>
-  <si>
-    <t>JU7E8w0nfKa</t>
-  </si>
-  <si>
-    <t>TmNT9yg49rF</t>
-  </si>
-  <si>
-    <t>iltdyT0Su5w</t>
-  </si>
-  <si>
-    <t>CdqOyNmMMWM</t>
-  </si>
-  <si>
-    <t>qyh3tf0o4fJ</t>
-  </si>
-  <si>
-    <t>YQM5ctsQN94</t>
-  </si>
-  <si>
-    <t>IfrydppWD9N</t>
-  </si>
-  <si>
-    <t>GvywHD6crky</t>
+    <t>UChfjD0hzCH</t>
+  </si>
+  <si>
+    <t>OMNXWu3iGdF</t>
+  </si>
+  <si>
+    <t>JFJbvs7lCvT</t>
+  </si>
+  <si>
+    <t>wH6eF5EOquE</t>
+  </si>
+  <si>
+    <t>ImXwGHlg2yv</t>
+  </si>
+  <si>
+    <t>ie8hYu42cek</t>
+  </si>
+  <si>
+    <t>KoPBpFtQdOu</t>
+  </si>
+  <si>
+    <t>aWh8R2JaC75</t>
+  </si>
+  <si>
+    <t>Q6FgKr2kuN9</t>
+  </si>
+  <si>
+    <t>BOkOhyKVIyc</t>
+  </si>
+  <si>
+    <t>zuuvMbheaJO</t>
+  </si>
+  <si>
+    <t>tbnuoG1cJmK</t>
+  </si>
+  <si>
+    <t>NFoBj156Lqe</t>
+  </si>
+  <si>
+    <t>TMLSNSXAO4p</t>
+  </si>
+  <si>
+    <t>WSSNiDjvQHQ</t>
+  </si>
+  <si>
+    <t>yePW20Gp2Qq</t>
+  </si>
+  <si>
+    <t>W07RQL0pUtD</t>
+  </si>
+  <si>
+    <t>e4Wnrf17qpG</t>
+  </si>
+  <si>
+    <t>dz866s8YpWK</t>
+  </si>
+  <si>
+    <t>vssNzfN9jm5</t>
+  </si>
+  <si>
+    <t>EAWW53f1o1q</t>
+  </si>
+  <si>
+    <t>JEJpZSAicYy</t>
+  </si>
+  <si>
+    <t>mL9yom2aC4t</t>
+  </si>
+  <si>
+    <t>WYmv9REEh9J</t>
+  </si>
+  <si>
+    <t>wyCMNxCrG0k</t>
+  </si>
+  <si>
+    <t>PWCFOb5D3JZ</t>
+  </si>
+  <si>
+    <t>MVioqGqZZGM</t>
+  </si>
+  <si>
+    <t>gzqOJdTPQ6C</t>
+  </si>
+  <si>
+    <t>kQNzrR5EhgE</t>
+  </si>
+  <si>
+    <t>kGo2cGmgv0m</t>
+  </si>
+  <si>
+    <t>h9ZPKhDJF7J</t>
+  </si>
+  <si>
+    <t>eXCxs5CXWn1</t>
+  </si>
+  <si>
+    <t>s4SazQqQ4II</t>
+  </si>
+  <si>
+    <t>XKmq1WKDxJU</t>
+  </si>
+  <si>
+    <t>tnsVx6PLhXi</t>
+  </si>
+  <si>
+    <t>khYQohZQnME</t>
+  </si>
+  <si>
+    <t>mPX5zXvavKc</t>
+  </si>
+  <si>
+    <t>ZTbuRLN7eBZ</t>
+  </si>
+  <si>
+    <t>UD0GV8cZ2H6</t>
+  </si>
+  <si>
+    <t>xm4rhhNZnCr</t>
+  </si>
+  <si>
+    <t>xFDOFDFoK0U</t>
+  </si>
+  <si>
+    <t>vPXAYNlDzcn</t>
+  </si>
+  <si>
+    <t>S08J1a9FmFV</t>
+  </si>
+  <si>
+    <t>jvK8HLFmi2D</t>
+  </si>
+  <si>
+    <t>v99eKotVVyC</t>
+  </si>
+  <si>
+    <t>UP2gbVW48rB</t>
+  </si>
+  <si>
+    <t>pd4DbTJY7Mj</t>
+  </si>
+  <si>
+    <t>DZslYveW6vC</t>
+  </si>
+  <si>
+    <t>IJpCemJT9gv</t>
+  </si>
+  <si>
+    <t>EzhYU09E6uQ</t>
+  </si>
+  <si>
+    <t>lS4Je8z2LSl</t>
+  </si>
+  <si>
+    <t>bUEVij8EgTP</t>
+  </si>
+  <si>
+    <t>B82xJvaCKdt</t>
+  </si>
+  <si>
+    <t>eIa4W414QzO</t>
+  </si>
+  <si>
+    <t>eUQ13G9JgEc</t>
+  </si>
+  <si>
+    <t>uP1H9tRVfxU</t>
+  </si>
+  <si>
+    <t>NNOc6iSS8mL</t>
+  </si>
+  <si>
+    <t>lbQHK2v2jsC</t>
+  </si>
+  <si>
+    <t>ZUSYSx4WTDK</t>
+  </si>
+  <si>
+    <t>YiN8QFFOnxX</t>
+  </si>
+  <si>
+    <t>Nqahzvh8P2e</t>
+  </si>
+  <si>
+    <t>sMOW9iHb3hY</t>
+  </si>
+  <si>
+    <t>GaCLGTYiJXk</t>
+  </si>
+  <si>
+    <t>H5ssuDCdXve</t>
+  </si>
+  <si>
+    <t>WOSmfAkQeqd</t>
+  </si>
+  <si>
+    <t>PtAJ8VJElPT</t>
+  </si>
+  <si>
+    <t>Q21JhUduMR1</t>
+  </si>
+  <si>
+    <t>mMcfVWgzNO9</t>
+  </si>
+  <si>
+    <t>Gu6055aWHbv</t>
+  </si>
+  <si>
+    <t>zzbLyDEi1kK</t>
+  </si>
+  <si>
+    <t>hGdgdpUufuc</t>
+  </si>
+  <si>
+    <t>WLxQRjoLKYG</t>
+  </si>
+  <si>
+    <t>TcoFnWMwTYS</t>
+  </si>
+  <si>
+    <t>uUveXvTUw7i</t>
+  </si>
+  <si>
+    <t>CalaaRBbNNe</t>
+  </si>
+  <si>
+    <t>Y561XDtq0rF</t>
+  </si>
+  <si>
+    <t>t1pYEpysPOB</t>
+  </si>
+  <si>
+    <t>ab5Xxq8lJYj</t>
+  </si>
+  <si>
+    <t>kN2CMQg4D4x</t>
+  </si>
+  <si>
+    <t>rMwzUZoYh00</t>
+  </si>
+  <si>
+    <t>zFYmQ8XFoLq</t>
+  </si>
+  <si>
+    <t>FrfMnZZspOk</t>
+  </si>
+  <si>
+    <t>rxw8ObsFaK1</t>
+  </si>
+  <si>
+    <t>Wy6x4eIq0X4</t>
+  </si>
+  <si>
+    <t>cozRXvz2IDw</t>
+  </si>
+  <si>
+    <t>jKI38FJ3j7s</t>
+  </si>
+  <si>
+    <t>rnA6j2Z3Clv</t>
+  </si>
+  <si>
+    <t>EoxkeelKRb1</t>
+  </si>
+  <si>
+    <t>VgNP7FHrvsA</t>
+  </si>
+  <si>
+    <t>YtzqVLGqKMz</t>
+  </si>
+  <si>
+    <t>LWqoxpnVNnc</t>
+  </si>
+  <si>
+    <t>binpVLeTUMT</t>
+  </si>
+  <si>
+    <t>cClSEbkTNp8</t>
+  </si>
+  <si>
+    <t>il79wKnSm1f</t>
+  </si>
+  <si>
+    <t>h6FkN9TE0XJ</t>
+  </si>
+  <si>
+    <t>sLcZm2CDqiU</t>
+  </si>
+  <si>
+    <t>Ry9LHejIGB1</t>
+  </si>
+  <si>
+    <t>T4H6ELymmd2</t>
+  </si>
+  <si>
+    <t>u0fxFMeS5xt</t>
+  </si>
+  <si>
+    <t>PZY7yW4dA5C</t>
+  </si>
+  <si>
+    <t>uOvhvu0UWRP</t>
+  </si>
+  <si>
+    <t>pOW88I6ZsFM</t>
+  </si>
+  <si>
+    <t>PqKTklojeiw</t>
+  </si>
+  <si>
+    <t>Iic3O4patYk</t>
+  </si>
+  <si>
+    <t>SDxsOgyldER</t>
+  </si>
+  <si>
+    <t>AiyUTVYb2Wk</t>
+  </si>
+  <si>
+    <t>uE9mLp5k0VI</t>
+  </si>
+  <si>
+    <t>zL5rT6L7WhF</t>
+  </si>
+  <si>
+    <t>nWGSLaG8Vp1</t>
+  </si>
+  <si>
+    <t>PRh8Ww7O7oQ</t>
+  </si>
+  <si>
+    <t>QpmPtwmpnzH</t>
+  </si>
+  <si>
+    <t>MwyWSlvbGW8</t>
+  </si>
+  <si>
+    <t>OuJpOjUEIhx</t>
+  </si>
+  <si>
+    <t>ffD8C8fVs34</t>
+  </si>
+  <si>
+    <t>zGKGLRZbMLN</t>
+  </si>
+  <si>
+    <t>J4g22FAMec5</t>
+  </si>
+  <si>
+    <t>HDb6Cqs140F</t>
+  </si>
+  <si>
+    <t>OEy0QMmsXrB</t>
+  </si>
+  <si>
+    <t>BiNk0tHpOdZ</t>
+  </si>
+  <si>
+    <t>lorD9x20dIw</t>
+  </si>
+  <si>
+    <t>VEqZ3fJuDd1</t>
+  </si>
+  <si>
+    <t>BomT5imfOsH</t>
+  </si>
+  <si>
+    <t>uH8VDyLV268</t>
+  </si>
+  <si>
+    <t>zoM9puHAEv2</t>
+  </si>
+  <si>
+    <t>hb4Y27RG1AA</t>
+  </si>
+  <si>
+    <t>dc89JhJ1osu</t>
+  </si>
+  <si>
+    <t>G4JSP9cA4u1</t>
+  </si>
+  <si>
+    <t>Fl1IKH8A3ZC</t>
+  </si>
+  <si>
+    <t>xQFXMIV0Y75</t>
+  </si>
+  <si>
+    <t>nts7AJz4d54</t>
+  </si>
+  <si>
+    <t>ev4bS4ZtQKx</t>
+  </si>
+  <si>
+    <t>A18nw8rbHKo</t>
+  </si>
+  <si>
+    <t>FLWziQpaQcE</t>
+  </si>
+  <si>
+    <t>Z1d5SZGgRSa</t>
+  </si>
+  <si>
+    <t>dk980H8oZRY</t>
+  </si>
+  <si>
+    <t>BAPw6BWQd7p</t>
+  </si>
+  <si>
+    <t>SlxTqGBLmXT</t>
+  </si>
+  <si>
+    <t>C3g6DwmpgEq</t>
+  </si>
+  <si>
+    <t>zOVDvxrsZN4</t>
+  </si>
+  <si>
+    <t>IHVocpE1AGu</t>
+  </si>
+  <si>
+    <t>qMGbTPqMBPP</t>
+  </si>
+  <si>
+    <t>OY0twmrNtRR</t>
+  </si>
+  <si>
+    <t>QIRUJAZ48Pq</t>
+  </si>
+  <si>
+    <t>ZUxiWeQZnvn</t>
+  </si>
+  <si>
+    <t>NuKBIDimql9</t>
+  </si>
+  <si>
+    <t>zpq1hKF5DZV</t>
+  </si>
+  <si>
+    <t>vpIzX6qhj8Y</t>
+  </si>
+  <si>
+    <t>PtsmpZwpwrM</t>
+  </si>
+  <si>
+    <t>F31MxIG42Pe</t>
+  </si>
+  <si>
+    <t>JWaEmz7pNrR</t>
+  </si>
+  <si>
+    <t>uveZaFnZywm</t>
+  </si>
+  <si>
+    <t>mXakT1Mh18C</t>
+  </si>
+  <si>
+    <t>OTUgYCkH77T</t>
+  </si>
+  <si>
+    <t>d52LXgOBExI</t>
+  </si>
+  <si>
+    <t>cMRCSHowl59</t>
+  </si>
+  <si>
+    <t>m9f31EhB2Xx</t>
+  </si>
+  <si>
+    <t>M6MtKUgsmdY</t>
+  </si>
+  <si>
+    <t>GR3JSQlLghA</t>
+  </si>
+  <si>
+    <t>M71dF6xgGzT</t>
+  </si>
+  <si>
+    <t>kFe2AGE8glo</t>
+  </si>
+  <si>
+    <t>zUBIISs54LK</t>
+  </si>
+  <si>
+    <t>AdAr82o9HRX</t>
+  </si>
+  <si>
+    <t>BKSlgVRWD2P</t>
+  </si>
+  <si>
+    <t>sXZkDqmvFyX</t>
+  </si>
+  <si>
+    <t>izVfk5ZP9RQ</t>
+  </si>
+  <si>
+    <t>dkz3q8gCbnL</t>
+  </si>
+  <si>
+    <t>Z1h3ff3CGyO</t>
+  </si>
+  <si>
+    <t>XAX3iL9pW9U</t>
+  </si>
+  <si>
+    <t>nmIGPT2a2g3</t>
+  </si>
+  <si>
+    <t>l0lJKgjsU2b</t>
+  </si>
+  <si>
+    <t>rdsD1vLqpCr</t>
+  </si>
+  <si>
+    <t>BZ108GtC4vM</t>
+  </si>
+  <si>
+    <t>uHlQCa36Onn</t>
+  </si>
+  <si>
+    <t>wRK0SFAHsbX</t>
+  </si>
+  <si>
+    <t>H8SJ5szd70U</t>
+  </si>
+  <si>
+    <t>K1a13hvNiy7</t>
+  </si>
+  <si>
+    <t>f4OWp6vC3SL</t>
+  </si>
+  <si>
+    <t>LPHbNVrN8sQ</t>
+  </si>
+  <si>
+    <t>qUOGQ5g8XAv</t>
+  </si>
+  <si>
+    <t>H1OJK9ULqjv</t>
+  </si>
+  <si>
+    <t>nrVmPjSwsNs</t>
+  </si>
+  <si>
+    <t>CbQNFv5ff0u</t>
+  </si>
+  <si>
+    <t>xxADche6IkH</t>
+  </si>
+  <si>
+    <t>k8EF45LLf30</t>
+  </si>
+  <si>
+    <t>TY4nFI1qL6L</t>
+  </si>
+  <si>
+    <t>vhz1qH1lED8</t>
+  </si>
+  <si>
+    <t>Mq4IWWHreth</t>
+  </si>
+  <si>
+    <t>o3aq2tZWmFR</t>
+  </si>
+  <si>
+    <t>mP7dLpeMFkC</t>
+  </si>
+  <si>
+    <t>NmNpjgwY5k4</t>
+  </si>
+  <si>
+    <t>aaUEMAhsFb3</t>
+  </si>
+  <si>
+    <t>hFhGeRuqvzf</t>
+  </si>
+  <si>
+    <t>kIfq0gRJ5bn</t>
+  </si>
+  <si>
+    <t>kq1ZesGAviW</t>
+  </si>
+  <si>
+    <t>kTU1VVfdFvk</t>
+  </si>
+  <si>
+    <t>VblNtzyEXDx</t>
+  </si>
+  <si>
+    <t>wjK7uSFRdNR</t>
+  </si>
+  <si>
+    <t>u3WmU8i29IY</t>
+  </si>
+  <si>
+    <t>QEZ4QJ0og53</t>
+  </si>
+  <si>
+    <t>v5UyPbIdEwg</t>
+  </si>
+  <si>
+    <t>lxE26Aq5fbR</t>
+  </si>
+  <si>
+    <t>PpUdRIBVXo7</t>
+  </si>
+  <si>
+    <t>jUr2hVHakZl</t>
+  </si>
+  <si>
+    <t>hsXPDGGSaYc</t>
+  </si>
+  <si>
+    <t>nBlqOxGPXZM</t>
+  </si>
+  <si>
+    <t>XyxL7sgyzCs</t>
+  </si>
+  <si>
+    <t>vJJ5UG5Lg6K</t>
+  </si>
+  <si>
+    <t>ToykQsUE6hY</t>
+  </si>
+  <si>
+    <t>SyL32ktW1ba</t>
+  </si>
+  <si>
+    <t>GIOVQ2DKFBC</t>
+  </si>
+  <si>
+    <t>qkXEboMv4Z8</t>
+  </si>
+  <si>
+    <t>KdfBS5bXEdN</t>
+  </si>
+  <si>
+    <t>u5Kv4DsHUKM</t>
+  </si>
+  <si>
+    <t>dtuNkYDIdKV</t>
+  </si>
+  <si>
+    <t>oP5WJm3eCpy</t>
+  </si>
+  <si>
+    <t>cpsP0Tyv9Y8</t>
+  </si>
+  <si>
+    <t>CtB30UhMTBo</t>
+  </si>
+  <si>
+    <t>AGbLSw28Jku</t>
+  </si>
+  <si>
+    <t>TX67lYVaadR</t>
+  </si>
+  <si>
+    <t>NrySRbs3Lc8</t>
+  </si>
+  <si>
+    <t>c9haYTtrvu8</t>
+  </si>
+  <si>
+    <t>gTz9xBPNfBj</t>
+  </si>
+  <si>
+    <t>DyqXCE5LXI0</t>
+  </si>
+  <si>
+    <t>Adq25z5dQsg</t>
+  </si>
+  <si>
+    <t>MKt0AMM97u7</t>
+  </si>
+  <si>
+    <t>gdCqrEkHfhf</t>
+  </si>
+  <si>
+    <t>e4KXmI33OAF</t>
+  </si>
+  <si>
+    <t>meXvFfsypCN</t>
+  </si>
+  <si>
+    <t>KHk2uwWbuLb</t>
+  </si>
+  <si>
+    <t>dlXyYPWM67j</t>
+  </si>
+  <si>
+    <t>TwWYpO65MH9</t>
+  </si>
+  <si>
+    <t>OAMQplqNYzi</t>
+  </si>
+  <si>
+    <t>kV99cNjMbUr</t>
+  </si>
+  <si>
+    <t>YYICnvbzxBj</t>
+  </si>
+  <si>
+    <t>H9aRd5LmHq3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +902,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="33">
@@ -639,10 +1250,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1019,15 +1633,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473396D4-529C-404F-BD23-A607D6373C22}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C603"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.54296875" customWidth="1"/>
     <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1038,357 +1652,2747 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
+      <c r="B33" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
-      </c>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C57" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C71" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C72" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C73" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C74" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C75" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C76" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C78" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C80" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C82" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C83" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C85" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C87" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C88" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C89" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C90" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C91" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C92" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C93" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C94" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C95" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C97" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C98" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C100" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C101" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C102" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>83</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C103" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C104" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>93</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C105" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>108</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C106" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>109</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C107" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>110</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C108" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>111</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C109" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>112</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C110" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>113</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C111" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>114</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C112" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>115</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C113" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>116</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C114" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>117</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C115" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>118</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C116" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>119</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C117" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>120</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C118" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="B119" s="2"/>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="B120" s="2"/>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="B121" s="2"/>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="B122" s="2"/>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="B123" s="2"/>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="B124" s="2"/>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="B125" s="2"/>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="B126" s="2"/>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="B127" s="2"/>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="B128" s="2"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="2"/>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="2"/>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" s="2"/>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132" s="2"/>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133" s="2"/>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134" s="2"/>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135" s="2"/>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" s="2"/>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" s="2"/>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138" s="2"/>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139" s="2"/>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140" s="2"/>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" s="2"/>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" s="2"/>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" s="2"/>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144" s="2"/>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" s="2"/>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" s="2"/>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="2"/>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" s="2"/>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" s="2"/>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150" s="2"/>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151" s="2"/>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152" s="2"/>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" s="2"/>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" s="2"/>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" s="2"/>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" s="2"/>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157" s="2"/>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" s="2"/>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159" s="2"/>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160" s="2"/>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="2"/>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="2"/>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" s="2"/>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" s="2"/>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165" s="2"/>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166" s="2"/>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" s="2"/>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" s="2"/>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" s="2"/>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" s="2"/>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" s="2"/>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" s="2"/>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" s="2"/>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174" s="2"/>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175" s="2"/>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176" s="2"/>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="2"/>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="2"/>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="2"/>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180" s="2"/>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" s="2"/>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182" s="2"/>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" s="2"/>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184" s="2"/>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" s="2"/>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186" s="2"/>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187" s="2"/>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" s="2"/>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189" s="2"/>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190" s="2"/>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191" s="2"/>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" s="2"/>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" s="2"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="2"/>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="2"/>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="2"/>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="2"/>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" s="2"/>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" s="2"/>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200" s="2"/>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201" s="2"/>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202" s="2"/>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" s="2"/>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204" s="2"/>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205" s="2"/>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206" s="2"/>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207" s="2"/>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208" s="2"/>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" s="2"/>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210" s="2"/>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" s="2"/>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" s="2"/>
+    </row>
+    <row r="213" spans="2:2">
+      <c r="B213" s="2"/>
+    </row>
+    <row r="214" spans="2:2">
+      <c r="B214" s="2"/>
+    </row>
+    <row r="215" spans="2:2">
+      <c r="B215" s="2"/>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" s="2"/>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217" s="2"/>
+    </row>
+    <row r="218" spans="2:2">
+      <c r="B218" s="2"/>
+    </row>
+    <row r="219" spans="2:2">
+      <c r="B219" s="2"/>
+    </row>
+    <row r="220" spans="2:2">
+      <c r="B220" s="2"/>
+    </row>
+    <row r="221" spans="2:2">
+      <c r="B221" s="2"/>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222" s="2"/>
+    </row>
+    <row r="223" spans="2:2">
+      <c r="B223" s="2"/>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="2"/>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" s="2"/>
+    </row>
+    <row r="226" spans="2:2">
+      <c r="B226" s="2"/>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" s="2"/>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" s="2"/>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" s="2"/>
+    </row>
+    <row r="230" spans="2:2">
+      <c r="B230" s="2"/>
+    </row>
+    <row r="231" spans="2:2">
+      <c r="B231" s="2"/>
+    </row>
+    <row r="232" spans="2:2">
+      <c r="B232" s="2"/>
+    </row>
+    <row r="233" spans="2:2">
+      <c r="B233" s="2"/>
+    </row>
+    <row r="234" spans="2:2">
+      <c r="B234" s="2"/>
+    </row>
+    <row r="235" spans="2:2">
+      <c r="B235" s="2"/>
+    </row>
+    <row r="236" spans="2:2">
+      <c r="B236" s="2"/>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237" s="2"/>
+    </row>
+    <row r="238" spans="2:2">
+      <c r="B238" s="2"/>
+    </row>
+    <row r="239" spans="2:2">
+      <c r="B239" s="2"/>
+    </row>
+    <row r="240" spans="2:2">
+      <c r="B240" s="2"/>
+    </row>
+    <row r="241" spans="2:2">
+      <c r="B241" s="2"/>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242" s="2"/>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" s="2"/>
+    </row>
+    <row r="244" spans="2:2">
+      <c r="B244" s="2"/>
+    </row>
+    <row r="245" spans="2:2">
+      <c r="B245" s="2"/>
+    </row>
+    <row r="246" spans="2:2">
+      <c r="B246" s="2"/>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247" s="2"/>
+    </row>
+    <row r="248" spans="2:2">
+      <c r="B248" s="2"/>
+    </row>
+    <row r="249" spans="2:2">
+      <c r="B249" s="2"/>
+    </row>
+    <row r="250" spans="2:2">
+      <c r="B250" s="2"/>
+    </row>
+    <row r="251" spans="2:2">
+      <c r="B251" s="2"/>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252" s="2"/>
+    </row>
+    <row r="253" spans="2:2">
+      <c r="B253" s="2"/>
+    </row>
+    <row r="254" spans="2:2">
+      <c r="B254" s="2"/>
+    </row>
+    <row r="255" spans="2:2">
+      <c r="B255" s="2"/>
+    </row>
+    <row r="256" spans="2:2">
+      <c r="B256" s="2"/>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257" s="2"/>
+    </row>
+    <row r="258" spans="2:2">
+      <c r="B258" s="2"/>
+    </row>
+    <row r="259" spans="2:2">
+      <c r="B259" s="2"/>
+    </row>
+    <row r="260" spans="2:2">
+      <c r="B260" s="2"/>
+    </row>
+    <row r="261" spans="2:2">
+      <c r="B261" s="2"/>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262" s="2"/>
+    </row>
+    <row r="263" spans="2:2">
+      <c r="B263" s="2"/>
+    </row>
+    <row r="264" spans="2:2">
+      <c r="B264" s="2"/>
+    </row>
+    <row r="265" spans="2:2">
+      <c r="B265" s="2"/>
+    </row>
+    <row r="266" spans="2:2">
+      <c r="B266" s="2"/>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267" s="2"/>
+    </row>
+    <row r="268" spans="2:2">
+      <c r="B268" s="2"/>
+    </row>
+    <row r="269" spans="2:2">
+      <c r="B269" s="2"/>
+    </row>
+    <row r="270" spans="2:2">
+      <c r="B270" s="2"/>
+    </row>
+    <row r="271" spans="2:2">
+      <c r="B271" s="2"/>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272" s="2"/>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" s="2"/>
+    </row>
+    <row r="274" spans="2:2">
+      <c r="B274" s="2"/>
+    </row>
+    <row r="275" spans="2:2">
+      <c r="B275" s="2"/>
+    </row>
+    <row r="276" spans="2:2">
+      <c r="B276" s="2"/>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277" s="2"/>
+    </row>
+    <row r="278" spans="2:2">
+      <c r="B278" s="2"/>
+    </row>
+    <row r="279" spans="2:2">
+      <c r="B279" s="2"/>
+    </row>
+    <row r="280" spans="2:2">
+      <c r="B280" s="2"/>
+    </row>
+    <row r="281" spans="2:2">
+      <c r="B281" s="2"/>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" s="2"/>
+    </row>
+    <row r="283" spans="2:2">
+      <c r="B283" s="2"/>
+    </row>
+    <row r="284" spans="2:2">
+      <c r="B284" s="2"/>
+    </row>
+    <row r="285" spans="2:2">
+      <c r="B285" s="2"/>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" s="2"/>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287" s="2"/>
+    </row>
+    <row r="288" spans="2:2">
+      <c r="B288" s="2"/>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" s="2"/>
+    </row>
+    <row r="290" spans="2:2">
+      <c r="B290" s="2"/>
+    </row>
+    <row r="291" spans="2:2">
+      <c r="B291" s="2"/>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292" s="2"/>
+    </row>
+    <row r="293" spans="2:2">
+      <c r="B293" s="2"/>
+    </row>
+    <row r="294" spans="2:2">
+      <c r="B294" s="2"/>
+    </row>
+    <row r="295" spans="2:2">
+      <c r="B295" s="2"/>
+    </row>
+    <row r="296" spans="2:2">
+      <c r="B296" s="2"/>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297" s="2"/>
+    </row>
+    <row r="298" spans="2:2">
+      <c r="B298" s="2"/>
+    </row>
+    <row r="299" spans="2:2">
+      <c r="B299" s="2"/>
+    </row>
+    <row r="300" spans="2:2">
+      <c r="B300" s="2"/>
+    </row>
+    <row r="301" spans="2:2">
+      <c r="B301" s="2"/>
+    </row>
+    <row r="302" spans="2:2">
+      <c r="B302" s="2"/>
+    </row>
+    <row r="303" spans="2:2">
+      <c r="B303" s="2"/>
+    </row>
+    <row r="304" spans="2:2">
+      <c r="B304" s="2"/>
+    </row>
+    <row r="305" spans="2:2">
+      <c r="B305" s="2"/>
+    </row>
+    <row r="306" spans="2:2">
+      <c r="B306" s="2"/>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307" s="2"/>
+    </row>
+    <row r="308" spans="2:2">
+      <c r="B308" s="2"/>
+    </row>
+    <row r="309" spans="2:2">
+      <c r="B309" s="2"/>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" s="2"/>
+    </row>
+    <row r="311" spans="2:2">
+      <c r="B311" s="2"/>
+    </row>
+    <row r="312" spans="2:2">
+      <c r="B312" s="2"/>
+    </row>
+    <row r="313" spans="2:2">
+      <c r="B313" s="2"/>
+    </row>
+    <row r="314" spans="2:2">
+      <c r="B314" s="2"/>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" s="2"/>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" s="2"/>
+    </row>
+    <row r="317" spans="2:2">
+      <c r="B317" s="2"/>
+    </row>
+    <row r="318" spans="2:2">
+      <c r="B318" s="2"/>
+    </row>
+    <row r="319" spans="2:2">
+      <c r="B319" s="2"/>
+    </row>
+    <row r="320" spans="2:2">
+      <c r="B320" s="2"/>
+    </row>
+    <row r="321" spans="2:2">
+      <c r="B321" s="2"/>
+    </row>
+    <row r="322" spans="2:2">
+      <c r="B322" s="2"/>
+    </row>
+    <row r="323" spans="2:2">
+      <c r="B323" s="2"/>
+    </row>
+    <row r="324" spans="2:2">
+      <c r="B324" s="2"/>
+    </row>
+    <row r="325" spans="2:2">
+      <c r="B325" s="2"/>
+    </row>
+    <row r="326" spans="2:2">
+      <c r="B326" s="2"/>
+    </row>
+    <row r="327" spans="2:2">
+      <c r="B327" s="2"/>
+    </row>
+    <row r="328" spans="2:2">
+      <c r="B328" s="2"/>
+    </row>
+    <row r="329" spans="2:2">
+      <c r="B329" s="2"/>
+    </row>
+    <row r="330" spans="2:2">
+      <c r="B330" s="2"/>
+    </row>
+    <row r="331" spans="2:2">
+      <c r="B331" s="2"/>
+    </row>
+    <row r="332" spans="2:2">
+      <c r="B332" s="2"/>
+    </row>
+    <row r="333" spans="2:2">
+      <c r="B333" s="2"/>
+    </row>
+    <row r="334" spans="2:2">
+      <c r="B334" s="2"/>
+    </row>
+    <row r="335" spans="2:2">
+      <c r="B335" s="2"/>
+    </row>
+    <row r="336" spans="2:2">
+      <c r="B336" s="2"/>
+    </row>
+    <row r="337" spans="2:2">
+      <c r="B337" s="2"/>
+    </row>
+    <row r="338" spans="2:2">
+      <c r="B338" s="2"/>
+    </row>
+    <row r="339" spans="2:2">
+      <c r="B339" s="2"/>
+    </row>
+    <row r="340" spans="2:2">
+      <c r="B340" s="2"/>
+    </row>
+    <row r="341" spans="2:2">
+      <c r="B341" s="2"/>
+    </row>
+    <row r="342" spans="2:2">
+      <c r="B342" s="2"/>
+    </row>
+    <row r="343" spans="2:2">
+      <c r="B343" s="2"/>
+    </row>
+    <row r="344" spans="2:2">
+      <c r="B344" s="2"/>
+    </row>
+    <row r="345" spans="2:2">
+      <c r="B345" s="2"/>
+    </row>
+    <row r="346" spans="2:2">
+      <c r="B346" s="2"/>
+    </row>
+    <row r="347" spans="2:2">
+      <c r="B347" s="2"/>
+    </row>
+    <row r="348" spans="2:2">
+      <c r="B348" s="2"/>
+    </row>
+    <row r="349" spans="2:2">
+      <c r="B349" s="2"/>
+    </row>
+    <row r="350" spans="2:2">
+      <c r="B350" s="2"/>
+    </row>
+    <row r="351" spans="2:2">
+      <c r="B351" s="2"/>
+    </row>
+    <row r="352" spans="2:2">
+      <c r="B352" s="2"/>
+    </row>
+    <row r="353" spans="2:2">
+      <c r="B353" s="2"/>
+    </row>
+    <row r="354" spans="2:2">
+      <c r="B354" s="2"/>
+    </row>
+    <row r="355" spans="2:2">
+      <c r="B355" s="2"/>
+    </row>
+    <row r="356" spans="2:2">
+      <c r="B356" s="2"/>
+    </row>
+    <row r="357" spans="2:2">
+      <c r="B357" s="2"/>
+    </row>
+    <row r="358" spans="2:2">
+      <c r="B358" s="2"/>
+    </row>
+    <row r="359" spans="2:2">
+      <c r="B359" s="2"/>
+    </row>
+    <row r="360" spans="2:2">
+      <c r="B360" s="2"/>
+    </row>
+    <row r="361" spans="2:2">
+      <c r="B361" s="2"/>
+    </row>
+    <row r="362" spans="2:2">
+      <c r="B362" s="2"/>
+    </row>
+    <row r="363" spans="2:2">
+      <c r="B363" s="2"/>
+    </row>
+    <row r="364" spans="2:2">
+      <c r="B364" s="2"/>
+    </row>
+    <row r="365" spans="2:2">
+      <c r="B365" s="2"/>
+    </row>
+    <row r="366" spans="2:2">
+      <c r="B366" s="2"/>
+    </row>
+    <row r="367" spans="2:2">
+      <c r="B367" s="2"/>
+    </row>
+    <row r="368" spans="2:2">
+      <c r="B368" s="2"/>
+    </row>
+    <row r="369" spans="2:2">
+      <c r="B369" s="2"/>
+    </row>
+    <row r="370" spans="2:2">
+      <c r="B370" s="2"/>
+    </row>
+    <row r="371" spans="2:2">
+      <c r="B371" s="2"/>
+    </row>
+    <row r="372" spans="2:2">
+      <c r="B372" s="2"/>
+    </row>
+    <row r="373" spans="2:2">
+      <c r="B373" s="2"/>
+    </row>
+    <row r="374" spans="2:2">
+      <c r="B374" s="2"/>
+    </row>
+    <row r="375" spans="2:2">
+      <c r="B375" s="2"/>
+    </row>
+    <row r="376" spans="2:2">
+      <c r="B376" s="2"/>
+    </row>
+    <row r="377" spans="2:2">
+      <c r="B377" s="2"/>
+    </row>
+    <row r="378" spans="2:2">
+      <c r="B378" s="2"/>
+    </row>
+    <row r="379" spans="2:2">
+      <c r="B379" s="2"/>
+    </row>
+    <row r="380" spans="2:2">
+      <c r="B380" s="2"/>
+    </row>
+    <row r="381" spans="2:2">
+      <c r="B381" s="2"/>
+    </row>
+    <row r="382" spans="2:2">
+      <c r="B382" s="2"/>
+    </row>
+    <row r="383" spans="2:2">
+      <c r="B383" s="2"/>
+    </row>
+    <row r="384" spans="2:2">
+      <c r="B384" s="2"/>
+    </row>
+    <row r="385" spans="2:2">
+      <c r="B385" s="2"/>
+    </row>
+    <row r="386" spans="2:2">
+      <c r="B386" s="2"/>
+    </row>
+    <row r="387" spans="2:2">
+      <c r="B387" s="2"/>
+    </row>
+    <row r="388" spans="2:2">
+      <c r="B388" s="2"/>
+    </row>
+    <row r="389" spans="2:2">
+      <c r="B389" s="2"/>
+    </row>
+    <row r="390" spans="2:2">
+      <c r="B390" s="2"/>
+    </row>
+    <row r="391" spans="2:2">
+      <c r="B391" s="2"/>
+    </row>
+    <row r="392" spans="2:2">
+      <c r="B392" s="2"/>
+    </row>
+    <row r="393" spans="2:2">
+      <c r="B393" s="2"/>
+    </row>
+    <row r="394" spans="2:2">
+      <c r="B394" s="2"/>
+    </row>
+    <row r="395" spans="2:2">
+      <c r="B395" s="2"/>
+    </row>
+    <row r="396" spans="2:2">
+      <c r="B396" s="2"/>
+    </row>
+    <row r="397" spans="2:2">
+      <c r="B397" s="2"/>
+    </row>
+    <row r="398" spans="2:2">
+      <c r="B398" s="2"/>
+    </row>
+    <row r="399" spans="2:2">
+      <c r="B399" s="2"/>
+    </row>
+    <row r="400" spans="2:2">
+      <c r="B400" s="2"/>
+    </row>
+    <row r="401" spans="2:2">
+      <c r="B401" s="2"/>
+    </row>
+    <row r="402" spans="2:2">
+      <c r="B402" s="2"/>
+    </row>
+    <row r="403" spans="2:2">
+      <c r="B403" s="2"/>
+    </row>
+    <row r="404" spans="2:2">
+      <c r="B404" s="2"/>
+    </row>
+    <row r="405" spans="2:2">
+      <c r="B405" s="2"/>
+    </row>
+    <row r="406" spans="2:2">
+      <c r="B406" s="2"/>
+    </row>
+    <row r="407" spans="2:2">
+      <c r="B407" s="2"/>
+    </row>
+    <row r="408" spans="2:2">
+      <c r="B408" s="2"/>
+    </row>
+    <row r="409" spans="2:2">
+      <c r="B409" s="2"/>
+    </row>
+    <row r="410" spans="2:2">
+      <c r="B410" s="2"/>
+    </row>
+    <row r="411" spans="2:2">
+      <c r="B411" s="2"/>
+    </row>
+    <row r="412" spans="2:2">
+      <c r="B412" s="2"/>
+    </row>
+    <row r="413" spans="2:2">
+      <c r="B413" s="2"/>
+    </row>
+    <row r="414" spans="2:2">
+      <c r="B414" s="2"/>
+    </row>
+    <row r="415" spans="2:2">
+      <c r="B415" s="2"/>
+    </row>
+    <row r="416" spans="2:2">
+      <c r="B416" s="2"/>
+    </row>
+    <row r="417" spans="2:2">
+      <c r="B417" s="2"/>
+    </row>
+    <row r="418" spans="2:2">
+      <c r="B418" s="2"/>
+    </row>
+    <row r="419" spans="2:2">
+      <c r="B419" s="2"/>
+    </row>
+    <row r="420" spans="2:2">
+      <c r="B420" s="2"/>
+    </row>
+    <row r="421" spans="2:2">
+      <c r="B421" s="2"/>
+    </row>
+    <row r="422" spans="2:2">
+      <c r="B422" s="2"/>
+    </row>
+    <row r="423" spans="2:2">
+      <c r="B423" s="2"/>
+    </row>
+    <row r="424" spans="2:2">
+      <c r="B424" s="2"/>
+    </row>
+    <row r="425" spans="2:2">
+      <c r="B425" s="2"/>
+    </row>
+    <row r="426" spans="2:2">
+      <c r="B426" s="2"/>
+    </row>
+    <row r="427" spans="2:2">
+      <c r="B427" s="2"/>
+    </row>
+    <row r="428" spans="2:2">
+      <c r="B428" s="2"/>
+    </row>
+    <row r="429" spans="2:2">
+      <c r="B429" s="2"/>
+    </row>
+    <row r="430" spans="2:2">
+      <c r="B430" s="2"/>
+    </row>
+    <row r="431" spans="2:2">
+      <c r="B431" s="2"/>
+    </row>
+    <row r="432" spans="2:2">
+      <c r="B432" s="2"/>
+    </row>
+    <row r="433" spans="2:2">
+      <c r="B433" s="2"/>
+    </row>
+    <row r="434" spans="2:2">
+      <c r="B434" s="2"/>
+    </row>
+    <row r="435" spans="2:2">
+      <c r="B435" s="2"/>
+    </row>
+    <row r="436" spans="2:2">
+      <c r="B436" s="2"/>
+    </row>
+    <row r="437" spans="2:2">
+      <c r="B437" s="2"/>
+    </row>
+    <row r="438" spans="2:2">
+      <c r="B438" s="2"/>
+    </row>
+    <row r="439" spans="2:2">
+      <c r="B439" s="2"/>
+    </row>
+    <row r="440" spans="2:2">
+      <c r="B440" s="2"/>
+    </row>
+    <row r="441" spans="2:2">
+      <c r="B441" s="2"/>
+    </row>
+    <row r="442" spans="2:2">
+      <c r="B442" s="2"/>
+    </row>
+    <row r="443" spans="2:2">
+      <c r="B443" s="2"/>
+    </row>
+    <row r="444" spans="2:2">
+      <c r="B444" s="2"/>
+    </row>
+    <row r="445" spans="2:2">
+      <c r="B445" s="2"/>
+    </row>
+    <row r="446" spans="2:2">
+      <c r="B446" s="2"/>
+    </row>
+    <row r="447" spans="2:2">
+      <c r="B447" s="2"/>
+    </row>
+    <row r="448" spans="2:2">
+      <c r="B448" s="2"/>
+    </row>
+    <row r="449" spans="2:2">
+      <c r="B449" s="2"/>
+    </row>
+    <row r="450" spans="2:2">
+      <c r="B450" s="2"/>
+    </row>
+    <row r="451" spans="2:2">
+      <c r="B451" s="2"/>
+    </row>
+    <row r="452" spans="2:2">
+      <c r="B452" s="2"/>
+    </row>
+    <row r="453" spans="2:2">
+      <c r="B453" s="2"/>
+    </row>
+    <row r="454" spans="2:2">
+      <c r="B454" s="2"/>
+    </row>
+    <row r="455" spans="2:2">
+      <c r="B455" s="2"/>
+    </row>
+    <row r="456" spans="2:2">
+      <c r="B456" s="2"/>
+    </row>
+    <row r="457" spans="2:2">
+      <c r="B457" s="2"/>
+    </row>
+    <row r="458" spans="2:2">
+      <c r="B458" s="2"/>
+    </row>
+    <row r="459" spans="2:2">
+      <c r="B459" s="2"/>
+    </row>
+    <row r="460" spans="2:2">
+      <c r="B460" s="2"/>
+    </row>
+    <row r="461" spans="2:2">
+      <c r="B461" s="2"/>
+    </row>
+    <row r="462" spans="2:2">
+      <c r="B462" s="2"/>
+    </row>
+    <row r="463" spans="2:2">
+      <c r="B463" s="2"/>
+    </row>
+    <row r="464" spans="2:2">
+      <c r="B464" s="2"/>
+    </row>
+    <row r="465" spans="2:2">
+      <c r="B465" s="2"/>
+    </row>
+    <row r="466" spans="2:2">
+      <c r="B466" s="2"/>
+    </row>
+    <row r="467" spans="2:2">
+      <c r="B467" s="2"/>
+    </row>
+    <row r="468" spans="2:2">
+      <c r="B468" s="2"/>
+    </row>
+    <row r="469" spans="2:2">
+      <c r="B469" s="2"/>
+    </row>
+    <row r="470" spans="2:2">
+      <c r="B470" s="2"/>
+    </row>
+    <row r="471" spans="2:2">
+      <c r="B471" s="2"/>
+    </row>
+    <row r="472" spans="2:2">
+      <c r="B472" s="2"/>
+    </row>
+    <row r="473" spans="2:2">
+      <c r="B473" s="2"/>
+    </row>
+    <row r="474" spans="2:2">
+      <c r="B474" s="2"/>
+    </row>
+    <row r="475" spans="2:2">
+      <c r="B475" s="2"/>
+    </row>
+    <row r="476" spans="2:2">
+      <c r="B476" s="2"/>
+    </row>
+    <row r="477" spans="2:2">
+      <c r="B477" s="2"/>
+    </row>
+    <row r="478" spans="2:2">
+      <c r="B478" s="2"/>
+    </row>
+    <row r="479" spans="2:2">
+      <c r="B479" s="2"/>
+    </row>
+    <row r="480" spans="2:2">
+      <c r="B480" s="2"/>
+    </row>
+    <row r="481" spans="2:2">
+      <c r="B481" s="2"/>
+    </row>
+    <row r="482" spans="2:2">
+      <c r="B482" s="2"/>
+    </row>
+    <row r="483" spans="2:2">
+      <c r="B483" s="2"/>
+    </row>
+    <row r="484" spans="2:2">
+      <c r="B484" s="2"/>
+    </row>
+    <row r="485" spans="2:2">
+      <c r="B485" s="2"/>
+    </row>
+    <row r="486" spans="2:2">
+      <c r="B486" s="2"/>
+    </row>
+    <row r="487" spans="2:2">
+      <c r="B487" s="2"/>
+    </row>
+    <row r="488" spans="2:2">
+      <c r="B488" s="2"/>
+    </row>
+    <row r="489" spans="2:2">
+      <c r="B489" s="2"/>
+    </row>
+    <row r="490" spans="2:2">
+      <c r="B490" s="2"/>
+    </row>
+    <row r="491" spans="2:2">
+      <c r="B491" s="2"/>
+    </row>
+    <row r="492" spans="2:2">
+      <c r="B492" s="2"/>
+    </row>
+    <row r="493" spans="2:2">
+      <c r="B493" s="2"/>
+    </row>
+    <row r="494" spans="2:2">
+      <c r="B494" s="2"/>
+    </row>
+    <row r="495" spans="2:2">
+      <c r="B495" s="2"/>
+    </row>
+    <row r="496" spans="2:2">
+      <c r="B496" s="2"/>
+    </row>
+    <row r="497" spans="2:2">
+      <c r="B497" s="2"/>
+    </row>
+    <row r="498" spans="2:2">
+      <c r="B498" s="2"/>
+    </row>
+    <row r="499" spans="2:2">
+      <c r="B499" s="2"/>
+    </row>
+    <row r="500" spans="2:2">
+      <c r="B500" s="2"/>
+    </row>
+    <row r="501" spans="2:2">
+      <c r="B501" s="2"/>
+    </row>
+    <row r="502" spans="2:2">
+      <c r="B502" s="2"/>
+    </row>
+    <row r="503" spans="2:2">
+      <c r="B503" s="2"/>
+    </row>
+    <row r="504" spans="2:2">
+      <c r="B504" s="2"/>
+    </row>
+    <row r="505" spans="2:2">
+      <c r="B505" s="2"/>
+    </row>
+    <row r="506" spans="2:2">
+      <c r="B506" s="2"/>
+    </row>
+    <row r="507" spans="2:2">
+      <c r="B507" s="2"/>
+    </row>
+    <row r="508" spans="2:2">
+      <c r="B508" s="2"/>
+    </row>
+    <row r="509" spans="2:2">
+      <c r="B509" s="2"/>
+    </row>
+    <row r="510" spans="2:2">
+      <c r="B510" s="2"/>
+    </row>
+    <row r="511" spans="2:2">
+      <c r="B511" s="2"/>
+    </row>
+    <row r="512" spans="2:2">
+      <c r="B512" s="2"/>
+    </row>
+    <row r="513" spans="2:2">
+      <c r="B513" s="2"/>
+    </row>
+    <row r="514" spans="2:2">
+      <c r="B514" s="2"/>
+    </row>
+    <row r="515" spans="2:2">
+      <c r="B515" s="2"/>
+    </row>
+    <row r="516" spans="2:2">
+      <c r="B516" s="2"/>
+    </row>
+    <row r="517" spans="2:2">
+      <c r="B517" s="2"/>
+    </row>
+    <row r="518" spans="2:2">
+      <c r="B518" s="2"/>
+    </row>
+    <row r="519" spans="2:2">
+      <c r="B519" s="2"/>
+    </row>
+    <row r="520" spans="2:2">
+      <c r="B520" s="2"/>
+    </row>
+    <row r="521" spans="2:2">
+      <c r="B521" s="2"/>
+    </row>
+    <row r="522" spans="2:2">
+      <c r="B522" s="2"/>
+    </row>
+    <row r="523" spans="2:2">
+      <c r="B523" s="2"/>
+    </row>
+    <row r="524" spans="2:2">
+      <c r="B524" s="2"/>
+    </row>
+    <row r="525" spans="2:2">
+      <c r="B525" s="2"/>
+    </row>
+    <row r="526" spans="2:2">
+      <c r="B526" s="2"/>
+    </row>
+    <row r="527" spans="2:2">
+      <c r="B527" s="2"/>
+    </row>
+    <row r="528" spans="2:2">
+      <c r="B528" s="2"/>
+    </row>
+    <row r="529" spans="2:2">
+      <c r="B529" s="2"/>
+    </row>
+    <row r="530" spans="2:2">
+      <c r="B530" s="2"/>
+    </row>
+    <row r="531" spans="2:2">
+      <c r="B531" s="2"/>
+    </row>
+    <row r="532" spans="2:2">
+      <c r="B532" s="2"/>
+    </row>
+    <row r="533" spans="2:2">
+      <c r="B533" s="2"/>
+    </row>
+    <row r="534" spans="2:2">
+      <c r="B534" s="2"/>
+    </row>
+    <row r="535" spans="2:2">
+      <c r="B535" s="2"/>
+    </row>
+    <row r="536" spans="2:2">
+      <c r="B536" s="2"/>
+    </row>
+    <row r="537" spans="2:2">
+      <c r="B537" s="2"/>
+    </row>
+    <row r="538" spans="2:2">
+      <c r="B538" s="2"/>
+    </row>
+    <row r="539" spans="2:2">
+      <c r="B539" s="2"/>
+    </row>
+    <row r="540" spans="2:2">
+      <c r="B540" s="2"/>
+    </row>
+    <row r="541" spans="2:2">
+      <c r="B541" s="2"/>
+    </row>
+    <row r="542" spans="2:2">
+      <c r="B542" s="2"/>
+    </row>
+    <row r="543" spans="2:2">
+      <c r="B543" s="2"/>
+    </row>
+    <row r="544" spans="2:2">
+      <c r="B544" s="2"/>
+    </row>
+    <row r="545" spans="2:2">
+      <c r="B545" s="2"/>
+    </row>
+    <row r="546" spans="2:2">
+      <c r="B546" s="2"/>
+    </row>
+    <row r="547" spans="2:2">
+      <c r="B547" s="2"/>
+    </row>
+    <row r="548" spans="2:2">
+      <c r="B548" s="2"/>
+    </row>
+    <row r="549" spans="2:2">
+      <c r="B549" s="2"/>
+    </row>
+    <row r="550" spans="2:2">
+      <c r="B550" s="2"/>
+    </row>
+    <row r="551" spans="2:2">
+      <c r="B551" s="2"/>
+    </row>
+    <row r="552" spans="2:2">
+      <c r="B552" s="2"/>
+    </row>
+    <row r="553" spans="2:2">
+      <c r="B553" s="2"/>
+    </row>
+    <row r="554" spans="2:2">
+      <c r="B554" s="2"/>
+    </row>
+    <row r="555" spans="2:2">
+      <c r="B555" s="2"/>
+    </row>
+    <row r="556" spans="2:2">
+      <c r="B556" s="2"/>
+    </row>
+    <row r="557" spans="2:2">
+      <c r="B557" s="2"/>
+    </row>
+    <row r="558" spans="2:2">
+      <c r="B558" s="2"/>
+    </row>
+    <row r="559" spans="2:2">
+      <c r="B559" s="2"/>
+    </row>
+    <row r="560" spans="2:2">
+      <c r="B560" s="2"/>
+    </row>
+    <row r="561" spans="2:2">
+      <c r="B561" s="2"/>
+    </row>
+    <row r="562" spans="2:2">
+      <c r="B562" s="2"/>
+    </row>
+    <row r="563" spans="2:2">
+      <c r="B563" s="2"/>
+    </row>
+    <row r="564" spans="2:2">
+      <c r="B564" s="2"/>
+    </row>
+    <row r="565" spans="2:2">
+      <c r="B565" s="2"/>
+    </row>
+    <row r="566" spans="2:2">
+      <c r="B566" s="2"/>
+    </row>
+    <row r="567" spans="2:2">
+      <c r="B567" s="2"/>
+    </row>
+    <row r="568" spans="2:2">
+      <c r="B568" s="2"/>
+    </row>
+    <row r="569" spans="2:2">
+      <c r="B569" s="2"/>
+    </row>
+    <row r="570" spans="2:2">
+      <c r="B570" s="2"/>
+    </row>
+    <row r="571" spans="2:2">
+      <c r="B571" s="2"/>
+    </row>
+    <row r="572" spans="2:2">
+      <c r="B572" s="2"/>
+    </row>
+    <row r="573" spans="2:2">
+      <c r="B573" s="2"/>
+    </row>
+    <row r="574" spans="2:2">
+      <c r="B574" s="2"/>
+    </row>
+    <row r="575" spans="2:2">
+      <c r="B575" s="2"/>
+    </row>
+    <row r="576" spans="2:2">
+      <c r="B576" s="2"/>
+    </row>
+    <row r="577" spans="2:2">
+      <c r="B577" s="2"/>
+    </row>
+    <row r="578" spans="2:2">
+      <c r="B578" s="2"/>
+    </row>
+    <row r="579" spans="2:2">
+      <c r="B579" s="2"/>
+    </row>
+    <row r="580" spans="2:2">
+      <c r="B580" s="2"/>
+    </row>
+    <row r="581" spans="2:2">
+      <c r="B581" s="2"/>
+    </row>
+    <row r="582" spans="2:2">
+      <c r="B582" s="2"/>
+    </row>
+    <row r="583" spans="2:2">
+      <c r="B583" s="2"/>
+    </row>
+    <row r="584" spans="2:2">
+      <c r="B584" s="2"/>
+    </row>
+    <row r="585" spans="2:2">
+      <c r="B585" s="2"/>
+    </row>
+    <row r="586" spans="2:2">
+      <c r="B586" s="2"/>
+    </row>
+    <row r="587" spans="2:2">
+      <c r="B587" s="2"/>
+    </row>
+    <row r="588" spans="2:2">
+      <c r="B588" s="2"/>
+    </row>
+    <row r="589" spans="2:2">
+      <c r="B589" s="2"/>
+    </row>
+    <row r="590" spans="2:2">
+      <c r="B590" s="2"/>
+    </row>
+    <row r="591" spans="2:2">
+      <c r="B591" s="2"/>
+    </row>
+    <row r="592" spans="2:2">
+      <c r="B592" s="2"/>
+    </row>
+    <row r="593" spans="2:2">
+      <c r="B593" s="2"/>
+    </row>
+    <row r="594" spans="2:2">
+      <c r="B594" s="2"/>
+    </row>
+    <row r="595" spans="2:2">
+      <c r="B595" s="2"/>
+    </row>
+    <row r="596" spans="2:2">
+      <c r="B596" s="2"/>
+    </row>
+    <row r="597" spans="2:2">
+      <c r="B597" s="2"/>
+    </row>
+    <row r="598" spans="2:2">
+      <c r="B598" s="2"/>
+    </row>
+    <row r="599" spans="2:2">
+      <c r="B599" s="2"/>
+    </row>
+    <row r="600" spans="2:2">
+      <c r="B600" s="2"/>
+    </row>
+    <row r="601" spans="2:2">
+      <c r="B601" s="2"/>
+    </row>
+    <row r="602" spans="2:2">
+      <c r="B602" s="2"/>
+    </row>
+    <row r="603" spans="2:2">
+      <c r="B603" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
